--- a/model_info/det_gpt_realset.xlsx
+++ b/model_info/det_gpt_realset.xlsx
@@ -393,7 +393,7 @@
         <v>1.0</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.7150400589194947</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.09444444444444444</v>
+        <v>0.4996031746031746</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.20927462217480713</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.075</v>
+        <v>0.3859848484848485</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.4434377333227159</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.624401890421459</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.6372377622377623</v>
+        <v>0.7582740535326742</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.375</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.4300899621212122</v>
+        <v>0.6525449810606061</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
     </row>
     <row r="10">
@@ -932,7 +932,7 @@
         <v>0.362027253439254</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.45662131993964766</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.15833333333333335</v>
+        <v>0.5599358974358974</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.25</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.06998275162337662</v>
+        <v>0.4490538758116883</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.8054984382550932</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.45708333333333345</v>
+        <v>0.7216923515981736</v>
       </c>
     </row>
     <row r="18">
@@ -1275,7 +1275,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.25</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.36705766336943857</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/det_gpt_realset.xlsx
+++ b/model_info/det_gpt_realset.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="5.5" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>1.0</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.7150400589194947</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.4996031746031746</v>
+        <v>0.08544973544973544</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.20927462217480713</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.3859848484848485</v>
+        <v>0.052272727272727276</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.4434377333227159</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.624401890421459</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.7582740535326742</v>
+        <v>0.5603297564504461</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.375</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.6525449810606061</v>
+        <v>0.3763287168560607</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
     </row>
     <row r="10">
@@ -932,7 +932,7 @@
         <v>0.362027253439254</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.45662131993964766</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.5599358974358974</v>
+        <v>0.15224358974358976</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.25</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.4490538758116883</v>
+        <v>0.05795446618810877</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.8054984382550932</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.7216923515981736</v>
+        <v>0.4508219178082193</v>
       </c>
     </row>
     <row r="18">
@@ -1275,7 +1275,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.25</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.36705766336943857</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
     </row>
   </sheetData>
